--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92523758337</v>
+        <v>46157.93089594594</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>8.4</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92452481744</v>
+        <v>46157.9297239903</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -19716,10 +19716,10 @@
         <v>0.01</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>46157.92452481744</v>
+        <v>46157.9297239903</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>46157.92452481744</v>
+        <v>46157.9297239903</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93089594594</v>
+        <v>46157.93354684132</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93354684132</v>
+        <v>46157.93645658019</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>8.4</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.9297239903</v>
+        <v>46157.93550865998</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -19716,10 +19716,10 @@
         <v>0.01</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>46157.9297239903</v>
+        <v>46157.93550865998</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>46157.9297239903</v>
+        <v>46157.93550865998</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93645658019</v>
+        <v>46158.28181297494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28181297494</v>
+        <v>46158.29755100714</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.93550865998</v>
+        <v>46158.29724380131</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -19716,10 +19716,10 @@
         <v>0.01</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>46157.93550865998</v>
+        <v>46158.29724380131</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>46157.93550865998</v>
+        <v>46158.29724380131</v>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29755100714</v>
+        <v>46158.29775400873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29775400873</v>
+        <v>46158.33343306197</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33343306197</v>
+        <v>46158.37202706226</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
